--- a/news_push_data/all_news/cna/20260402 中央社新聞.xlsx
+++ b/news_push_data/all_news/cna/20260402 中央社新聞.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>伊朗戰爭支持率狂瀉48百分點！傳統共和黨人轉向反戰</t>
+          <t>伊朗戰爭支持率狂瀉48百分點 傳統共和黨人轉向反戰</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -505,7 +505,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>伊朗總統致信美國民眾 溫情攻勢質疑川普師出無名</t>
+          <t>伊朗總統致信美國民眾 質疑川普師出無名</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>馬克宏會見高市早苗 互擺「龜派氣功」姿勢網路瘋傳</t>
+          <t>馬克宏會見高市早苗 互擺「龜派氣功」姿勢網路瘋傳[影]</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1790,519 +1790,6 @@
       <c r="E51" t="inlineStr">
         <is>
           <t>https://www.cna.com.tw/news/aopl/202604010105.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>中央社</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>中東戰爭第32天》美擬2、3週內結束伊朗戰事 最新發展一次看</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2026/04/01 11:39</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2026-04-01T11:39:00+08:00</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>https://www.cna.com.tw/news/aopl/202604010091.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>中央社</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>日航與全日空將漲燃油附加費 飛台灣漲幅逾50%</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2026/04/01 11:32</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2026-04-01T11:32:00+08:00</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>https://www.cna.com.tw/news/aopl/202604010078.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>中央社</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>盧比歐：伊朗戰爭終點在望 美戰後將審視與北約關係</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2026/04/01 11:30</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2026-04-01T11:30:00+08:00</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>https://www.cna.com.tw/news/aopl/202604010076.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>中央社</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>美法官下令停建白宮大宴會廳 川普政府火速提上訴</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2026/04/01 11:17</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2026-04-01T11:17:00+08:00</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>https://www.cna.com.tw/news/aopl/202604010074.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>中央社</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>甲骨文出手裁數千人 加碼AI對抗雲端強敵</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2026/04/01 10:46</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2026-04-01T10:46:00+08:00</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>https://www.cna.com.tw/news/aopl/202604010061.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>中央社</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>因應燃料危機 澳洲2州祭大眾運輸免費優惠</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2026/04/01 10:37</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2026-04-01T10:37:00+08:00</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>https://www.cna.com.tw/news/aopl/202604010056.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>中央社</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>油價飆漲 民調：約66%美國人盼儘快結束伊朗戰爭</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2026/04/01 10:25</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2026-04-01T10:25:00+08:00</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>https://www.cna.com.tw/news/aopl/202604010050.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>中央社</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>聯合國：中東戰爭恐吞噬阿拉伯國家2025年經濟成長</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2026/04/01 09:50</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2026-04-01T09:50:00+08:00</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>https://www.cna.com.tw/news/aopl/202604010042.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>中央社</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>日本茨城縣發生規模5.0地震 未引發海嘯</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2026/04/01 09:42</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2026-04-01T09:42:00+08:00</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>https://www.cna.com.tw/news/aopl/202604010039.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>中央社</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>開普敦幫派衝突11天83死 800名士兵將部署當地</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2026/04/01 08:56</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2026-04-01T08:56:00+08:00</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>https://www.cna.com.tw/news/aopl/202604010028.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>中央社</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>微軟攜手雪佛龍及Engine No. 1 簽訂供電協議</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2026/04/01 08:46</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2026-04-01T08:46:00+08:00</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>https://www.cna.com.tw/news/aopl/202604010027.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>中央社</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>川普：無論有無協議 美國將在2、3週內撤離伊朗</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2026/04/01 08:44</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2026-04-01T08:44:00+08:00</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>https://www.cna.com.tw/news/aopl/202604010026.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>中央社</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>美人道放行 俄油輪到港73萬桶原油暫解古巴危機</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2026/04/01 08:35</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2026-04-01T08:35:00+08:00</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>https://www.cna.com.tw/news/aopl/202604010023.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>中央社</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>馬斯克批加拿大虛偽不公平 再度惹惱加拿大人</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>2026/04/01 08:33</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2026-04-01T08:33:00+08:00</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>https://www.cna.com.tw/news/aopl/202604010022.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>中央社</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>美參議員將提案擴大中國車禁令 籲其他國家跟進</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2026/04/01 08:31</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2026-04-01T08:31:00+08:00</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>https://www.cna.com.tw/news/aopl/202604010021.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>中央社</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>俄軍用運輸機撞山壁墜毀29死 初判技術故障所致</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2026/04/01 08:26</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>2026-04-01T08:26:00+08:00</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>https://www.cna.com.tw/news/aopl/202604010020.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>中央社</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>義大利電影城公布亮眼財報 將製作刺客教條等大片</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>2026/04/01 07:43</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>2026-04-01T07:43:00+08:00</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>https://www.cna.com.tw/news/aopl/202604010017.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>中央社</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>中東局勢難解 高油價燒向美國</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>2026/04/01 07:25</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>2026-04-01T07:25:00+08:00</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>https://www.cna.com.tw/news/aopl/202604010016.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>中央社</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>川普挑戰出生公民權憲法修正案 最高法院見真章</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>2026/04/01 07:22</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>2026-04-01T07:22:00+08:00</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>https://www.cna.com.tw/news/aopl/202604010015.aspx</t>
         </is>
       </c>
     </row>
